--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_39.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2253719.236885475</v>
+        <v>2246786.835085624</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9630586.081252649</v>
+        <v>9630586.081252648</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9630586.081252649</v>
+        <v>9630586.081252648</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203521.3732441023</v>
+        <v>203521.3732441029</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203521.3732441023</v>
+        <v>203521.3732441029</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16960994.28247355</v>
+        <v>16960994.28247354</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -739,13 +739,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>170.1516951478432</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -790,13 +790,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>385</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>115.1034760716101</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -851,7 +851,7 @@
         <v>171.1850752716849</v>
       </c>
       <c r="O4" t="n">
-        <v>238.8543934329591</v>
+        <v>240.445564079015</v>
       </c>
       <c r="P4" t="n">
         <v>287.4478973282775</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -973,25 +973,25 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>184.0484016106927</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.338019733153826</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>32.46356367243068</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>167.1158402638076</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>112.0691552915769</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751173264</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1380,13 +1380,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U12" t="n">
         <v>50.21035976018675</v>
@@ -1729,19 +1729,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T15" t="n">
-        <v>118.0355277429563</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
         <v>50.21035976018675</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
         <v>82.37314290982852</v>
@@ -1857,10 +1857,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1984,10 +1984,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135.964704340989</v>
+        <v>131.9993129555745</v>
       </c>
       <c r="C20" t="n">
         <v>99.47457824299391</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G23" t="n">
         <v>53.75737228701621</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2398,7 +2398,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
@@ -2455,10 +2455,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2744,16 +2744,16 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>269.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>264.5481307876465</v>
       </c>
       <c r="Q28" t="n">
-        <v>419.2023219415596</v>
+        <v>423.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>424.6021279811511</v>
@@ -2808,7 +2808,7 @@
         <v>106.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>7.224591385414625</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2847,7 +2847,7 @@
         <v>347.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>335.0756155522384</v>
+        <v>327.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>336.3734759809475</v>
@@ -2975,28 +2975,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>121.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>218.6316114025499</v>
+        <v>204.174651084791</v>
       </c>
       <c r="N31" t="n">
-        <v>269.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>385.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>118.1773130341041</v>
+        <v>423.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>424.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>60.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,10 +3042,10 @@
         <v>101.7573722870162</v>
       </c>
       <c r="H32" t="n">
-        <v>106.0096587035274</v>
+        <v>113.234250088942</v>
       </c>
       <c r="I32" t="n">
-        <v>7.224591385414625</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>121.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3221,16 +3221,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>338.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>264.5481307876465</v>
       </c>
       <c r="Q34" t="n">
         <v>423.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>229.1570665320034</v>
+        <v>424.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3346,10 +3346,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>262.0138729201192</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3516,7 +3516,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3583,7 +3583,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,13 +3625,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>277.7834726314007</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>120.0978408452537</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
         <v>50.21035976018675</v>
@@ -3820,16 +3820,16 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>70.00566530352997</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>136.3296194165495</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4054,7 +4054,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>11.09991244551929</v>
+        <v>91.60958778454074</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4120,7 +4120,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
         <v>30.8</v>
@@ -4324,49 +4324,49 @@
         <v>411.95</v>
       </c>
       <c r="K2" t="n">
-        <v>777.6999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="L2" t="n">
-        <v>777.6999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="M2" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="N2" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="O2" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
       </c>
       <c r="R2" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="C3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>545.7373105916365</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>373.8669114524009</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4421,31 +4421,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S3" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>401.106331919057</v>
       </c>
       <c r="V3" t="n">
-        <v>949.9530371097363</v>
+        <v>386.4490923316629</v>
       </c>
       <c r="W3" t="n">
-        <v>917.2528927563742</v>
+        <v>270.182954885592</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577.3895764229453</v>
+        <v>1182.849945845151</v>
       </c>
       <c r="C4" t="n">
-        <v>580.6932364627121</v>
+        <v>1308.851951663587</v>
       </c>
       <c r="D4" t="n">
-        <v>694.0123805877122</v>
+        <v>1422.171095788587</v>
       </c>
       <c r="E4" t="n">
-        <v>694.0123805877122</v>
+        <v>1540</v>
       </c>
       <c r="F4" t="n">
-        <v>694.0123805877122</v>
+        <v>1540</v>
       </c>
       <c r="G4" t="n">
-        <v>847.4189464745974</v>
+        <v>1540</v>
       </c>
       <c r="H4" t="n">
-        <v>847.4189464745974</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1540</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4494,37 +4494,37 @@
         <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>68.05025509417312</v>
+        <v>191.3890126917233</v>
       </c>
       <c r="U4" t="n">
-        <v>314.6014477324597</v>
+        <v>437.94020533001</v>
       </c>
       <c r="V4" t="n">
-        <v>314.6014477324597</v>
+        <v>636.7615982159559</v>
       </c>
       <c r="W4" t="n">
-        <v>314.6014477324597</v>
+        <v>808.6525164756333</v>
       </c>
       <c r="X4" t="n">
-        <v>465.6322387566532</v>
+        <v>959.6833074998268</v>
       </c>
       <c r="Y4" t="n">
-        <v>465.6322387566532</v>
+        <v>1071.092608178859</v>
       </c>
     </row>
     <row r="5">
@@ -4567,16 +4567,16 @@
         <v>30.8</v>
       </c>
       <c r="M5" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="N5" t="n">
-        <v>793.0999999999999</v>
+        <v>396.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1174.25</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C6" t="n">
-        <v>711.2820432047779</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D6" t="n">
-        <v>359.8298342171994</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E6" t="n">
-        <v>359.8298342171994</v>
+        <v>376.2285475464957</v>
       </c>
       <c r="F6" t="n">
-        <v>359.8298342171994</v>
+        <v>33.16163609409477</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>33.16163609409477</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8</v>
+        <v>33.16163609409477</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S6" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T6" t="n">
-        <v>964.8227613033797</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U6" t="n">
-        <v>964.6102766971304</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V6" t="n">
-        <v>949.9530371097363</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W6" t="n">
-        <v>917.2528927563742</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X6" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y6" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>613.8032314979174</v>
+        <v>637.5231570163306</v>
       </c>
       <c r="C7" t="n">
-        <v>613.8032314979174</v>
+        <v>637.5231570163306</v>
       </c>
       <c r="D7" t="n">
-        <v>613.8032314979174</v>
+        <v>750.8423011413307</v>
       </c>
       <c r="E7" t="n">
-        <v>731.6321357093304</v>
+        <v>750.8423011413307</v>
       </c>
       <c r="F7" t="n">
-        <v>855.9931083012659</v>
+        <v>750.8423011413307</v>
       </c>
       <c r="G7" t="n">
-        <v>1009.399674188151</v>
+        <v>750.8423011413307</v>
       </c>
       <c r="H7" t="n">
-        <v>1178.916259347549</v>
+        <v>920.3588863007283</v>
       </c>
       <c r="I7" t="n">
-        <v>1178.916259347549</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4752,16 +4752,16 @@
         <v>314.6014477324597</v>
       </c>
       <c r="V7" t="n">
-        <v>330.5030125592077</v>
+        <v>314.6014477324597</v>
       </c>
       <c r="W7" t="n">
-        <v>502.3939308188852</v>
+        <v>486.4923659921371</v>
       </c>
       <c r="X7" t="n">
-        <v>502.3939308188852</v>
+        <v>637.5231570163306</v>
       </c>
       <c r="Y7" t="n">
-        <v>613.8032314979174</v>
+        <v>637.5231570163306</v>
       </c>
     </row>
     <row r="8">
@@ -4786,10 +4786,10 @@
         <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>508.7485532697942</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>144.0011669611888</v>
+        <v>728.3856405248639</v>
       </c>
       <c r="D9" t="n">
-        <v>144.0011669611888</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="E9" t="n">
         <v>30.8</v>
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>377.4367917426227</v>
+        <v>517.3876534589814</v>
       </c>
       <c r="C10" t="n">
-        <v>503.4387975610585</v>
+        <v>643.3896592774172</v>
       </c>
       <c r="D10" t="n">
-        <v>503.4387975610585</v>
+        <v>643.3896592774172</v>
       </c>
       <c r="E10" t="n">
-        <v>621.2677017724716</v>
+        <v>761.2185634888302</v>
       </c>
       <c r="F10" t="n">
-        <v>745.6286743644071</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G10" t="n">
-        <v>899.0352402512923</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H10" t="n">
-        <v>1068.55182541069</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.55182541069</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063141</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.00000000001</v>
+        <v>1540</v>
       </c>
       <c r="L10" t="n">
         <v>1517.821760089168</v>
@@ -4989,16 +4989,16 @@
         <v>256.125934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>377.4367917426227</v>
+        <v>256.125934252978</v>
       </c>
       <c r="W10" t="n">
-        <v>377.4367917426227</v>
+        <v>405.6303157926893</v>
       </c>
       <c r="X10" t="n">
-        <v>377.4367917426227</v>
+        <v>405.6303157926893</v>
       </c>
       <c r="Y10" t="n">
-        <v>377.4367917426227</v>
+        <v>405.6303157926893</v>
       </c>
     </row>
     <row r="11">
@@ -5023,10 +5023,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
@@ -5041,16 +5041,16 @@
         <v>1542.849113037656</v>
       </c>
       <c r="M11" t="n">
-        <v>1542.849113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N11" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H12" t="n">
         <v>44.72</v>
@@ -5132,31 +5132,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>937.5750872192207</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S12" t="n">
-        <v>819.8336731135527</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T12" t="n">
-        <v>410.3813850150538</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U12" t="n">
-        <v>359.6638499037541</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V12" t="n">
-        <v>294.5015598113094</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W12" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X12" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="13">
@@ -5269,25 +5269,25 @@
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>555.568828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N14" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O14" t="n">
-        <v>1662.388828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P14" t="n">
-        <v>2215.798828728935</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5372,16 +5372,16 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T15" t="n">
-        <v>763.9167385504073</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U15" t="n">
-        <v>713.1992034391076</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V15" t="n">
         <v>294.5015598113094</v>
@@ -5500,28 +5500,28 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1151.54</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="N17" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="O17" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1797.400904947332</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>1797.400904947332</v>
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
         <v>44.72</v>
@@ -5627,10 +5627,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5719,49 +5719,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1151.54</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>1662.388828728935</v>
+        <v>436.0291130376558</v>
       </c>
       <c r="N20" t="n">
-        <v>2215.798828728935</v>
+        <v>989.4391130376557</v>
       </c>
       <c r="O20" t="n">
-        <v>2215.798828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1508.625837177891</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C21" t="n">
-        <v>1143.878450869285</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
-        <v>1143.878450869285</v>
+        <v>44.72</v>
       </c>
       <c r="E21" t="n">
-        <v>1143.878450869285</v>
+        <v>44.72</v>
       </c>
       <c r="F21" t="n">
-        <v>1143.878450869285</v>
+        <v>44.72</v>
       </c>
       <c r="G21" t="n">
-        <v>1143.878450869285</v>
+        <v>44.72</v>
       </c>
       <c r="H21" t="n">
-        <v>1143.878450869285</v>
+        <v>44.72</v>
       </c>
       <c r="I21" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="J21" t="n">
-        <v>1204.524099806763</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K21" t="n">
-        <v>1393.716915901147</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>1665.067377496347</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M21" t="n">
-        <v>1751.147919239206</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N21" t="n">
-        <v>1884.428203846775</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2123.470655530493</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2036.733538088506</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>1918.992123982838</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>1863.075189419693</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>1812.357654308393</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>1747.195364215948</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>1663.990169357536</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>1593.421745675326</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>1543.531449951958</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
         <v>157.615990899539</v>
@@ -5980,22 +5980,22 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>1108.978828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>1108.978828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="O23" t="n">
-        <v>1662.388828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U24" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
         <v>274.6072361907174</v>
       </c>
       <c r="X24" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="25">
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
         <v>1078.695883794875</v>
@@ -6174,16 +6174,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6220,19 +6220,19 @@
         <v>58.64</v>
       </c>
       <c r="K26" t="n">
-        <v>768.3463663478684</v>
+        <v>58.64</v>
       </c>
       <c r="L26" t="n">
-        <v>1494.016366347868</v>
+        <v>58.64</v>
       </c>
       <c r="M26" t="n">
-        <v>1494.016366347868</v>
+        <v>569.488828728935</v>
       </c>
       <c r="N26" t="n">
-        <v>2107.236686122631</v>
+        <v>1182.709148503698</v>
       </c>
       <c r="O26" t="n">
-        <v>2493.400904947332</v>
+        <v>1908.379148503698</v>
       </c>
       <c r="P26" t="n">
         <v>2493.400904947332</v>
@@ -6308,7 +6308,7 @@
         <v>729.2203396077417</v>
       </c>
       <c r="N27" t="n">
-        <v>862.50062421531</v>
+        <v>1110.456065622884</v>
       </c>
       <c r="O27" t="n">
         <v>1349.498517306602</v>
@@ -6387,13 +6387,13 @@
         <v>1182.871843630703</v>
       </c>
       <c r="N28" t="n">
-        <v>910.9677271946573</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="O28" t="n">
-        <v>910.9677271946573</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="P28" t="n">
-        <v>910.9677271946573</v>
+        <v>915.6515095017668</v>
       </c>
       <c r="Q28" t="n">
         <v>487.5310383647991</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>734.2295790790585</v>
+        <v>741.5271461350328</v>
       </c>
       <c r="C29" t="n">
-        <v>585.2653586315898</v>
+        <v>592.5629256875642</v>
       </c>
       <c r="D29" t="n">
-        <v>475.8318679852769</v>
+        <v>483.1294350412513</v>
       </c>
       <c r="E29" t="n">
-        <v>372.4346057561166</v>
+        <v>379.732172812091</v>
       </c>
       <c r="F29" t="n">
-        <v>268.505687869236</v>
+        <v>275.8032549252104</v>
       </c>
       <c r="G29" t="n">
-        <v>165.7204633368964</v>
+        <v>173.0180303928707</v>
       </c>
       <c r="H29" t="n">
-        <v>58.64</v>
+        <v>65.93756705597437</v>
       </c>
       <c r="I29" t="n">
         <v>58.64</v>
@@ -6457,19 +6457,19 @@
         <v>449.9491130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>643.6617564436343</v>
+        <v>449.9491130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>643.6617564436343</v>
+        <v>449.9491130376557</v>
       </c>
       <c r="M29" t="n">
-        <v>1154.510585172569</v>
+        <v>960.7979417665907</v>
       </c>
       <c r="N29" t="n">
+        <v>1574.018261541354</v>
+      </c>
+      <c r="O29" t="n">
         <v>1767.730904947332</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2493.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>2493.400904947332</v>
@@ -6490,16 +6490,16 @@
         <v>2098.924195879295</v>
       </c>
       <c r="V29" t="n">
-        <v>1760.463978149762</v>
+        <v>1767.761545205736</v>
       </c>
       <c r="W29" t="n">
-        <v>1420.692790290219</v>
+        <v>1427.990357346193</v>
       </c>
       <c r="X29" t="n">
-        <v>1127.478817097625</v>
+        <v>1134.776384153599</v>
       </c>
       <c r="Y29" t="n">
-        <v>916.0470669129721</v>
+        <v>923.3446339689465</v>
       </c>
     </row>
     <row r="30">
@@ -6618,25 +6618,25 @@
         <v>1182.871843630703</v>
       </c>
       <c r="L31" t="n">
-        <v>1060.096461653148</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="M31" t="n">
-        <v>839.2564501354207</v>
+        <v>976.6348223329339</v>
       </c>
       <c r="N31" t="n">
-        <v>567.3523336993753</v>
+        <v>976.6348223329339</v>
       </c>
       <c r="O31" t="n">
-        <v>567.3523336993753</v>
+        <v>976.6348223329339</v>
       </c>
       <c r="P31" t="n">
-        <v>178.0110232667718</v>
+        <v>976.6348223329339</v>
       </c>
       <c r="Q31" t="n">
-        <v>58.64</v>
+        <v>548.5143511959662</v>
       </c>
       <c r="R31" t="n">
-        <v>58.64</v>
+        <v>119.6233128311671</v>
       </c>
       <c r="S31" t="n">
         <v>58.64</v>
@@ -6685,7 +6685,7 @@
         <v>173.0180303928707</v>
       </c>
       <c r="H32" t="n">
-        <v>65.93756705597437</v>
+        <v>58.64</v>
       </c>
       <c r="I32" t="n">
         <v>58.64</v>
@@ -6694,22 +6694,22 @@
         <v>58.64</v>
       </c>
       <c r="K32" t="n">
-        <v>58.64</v>
+        <v>768.3463663478684</v>
       </c>
       <c r="L32" t="n">
-        <v>784.3099999999999</v>
+        <v>1494.016366347868</v>
       </c>
       <c r="M32" t="n">
-        <v>784.3099999999999</v>
+        <v>2004.865195076804</v>
       </c>
       <c r="N32" t="n">
-        <v>1042.060904947332</v>
+        <v>2618.085514851567</v>
       </c>
       <c r="O32" t="n">
-        <v>1767.730904947332</v>
+        <v>2932</v>
       </c>
       <c r="P32" t="n">
-        <v>2493.400904947332</v>
+        <v>2932</v>
       </c>
       <c r="Q32" t="n">
         <v>2932</v>
@@ -6782,7 +6782,7 @@
         <v>729.2203396077417</v>
       </c>
       <c r="N33" t="n">
-        <v>862.50062421531</v>
+        <v>1110.456065622884</v>
       </c>
       <c r="O33" t="n">
         <v>1349.498517306602</v>
@@ -6855,22 +6855,22 @@
         <v>1182.871843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>1060.096461653148</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="M34" t="n">
-        <v>1060.096461653148</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="N34" t="n">
-        <v>1060.096461653148</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>718.2322555127287</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="P34" t="n">
-        <v>718.2322555127287</v>
+        <v>915.6515095017668</v>
       </c>
       <c r="Q34" t="n">
-        <v>290.111784375761</v>
+        <v>487.5310383647991</v>
       </c>
       <c r="R34" t="n">
         <v>58.64</v>
@@ -6928,25 +6928,25 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K35" t="n">
-        <v>989.4391130376558</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L35" t="n">
-        <v>989.4391130376558</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M35" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N35" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>935.4919426714454</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>817.7505285657774</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>761.8335940026321</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>711.1160588913324</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>645.9537687988877</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>562.7485739404751</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="37">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
         <v>44.72</v>
@@ -7177,40 +7177,40 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N38" t="n">
-        <v>1129.18</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O38" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>407.3842417608302</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C39" t="n">
-        <v>396.1722089875784</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>919.5630540741914</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>801.8216399685234</v>
       </c>
       <c r="T39" t="n">
-        <v>761.8335940026321</v>
+        <v>745.9047054053782</v>
       </c>
       <c r="U39" t="n">
-        <v>711.1160588913324</v>
+        <v>695.1871702940784</v>
       </c>
       <c r="V39" t="n">
-        <v>645.9537687988877</v>
+        <v>630.0248802016338</v>
       </c>
       <c r="W39" t="n">
-        <v>562.7485739404751</v>
+        <v>546.8196853432211</v>
       </c>
       <c r="X39" t="n">
-        <v>492.1801502582655</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y39" t="n">
-        <v>442.2898545348975</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="40">
@@ -7299,16 +7299,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
         <v>1153.55685638681</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7402,22 +7402,22 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M41" t="n">
-        <v>1129.18</v>
+        <v>1682.59</v>
       </c>
       <c r="N41" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="O41" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
         <v>2236</v>
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.9618669904511</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>373.7498342171993</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E42" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F42" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
         <v>44.72</v>
@@ -7526,7 +7526,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>419.8674797645184</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7642,19 +7642,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M44" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N44" t="n">
-        <v>946.8779417665908</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>1797.400904947332</v>
@@ -7663,7 +7663,7 @@
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
         <v>2085.68327354774</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7754,16 +7754,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907175</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="46">
@@ -7773,31 +7773,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K46" t="n">
         <v>1921.561060958496</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -7967,13 +7967,13 @@
         <v>420.0430062450903</v>
       </c>
       <c r="K2" t="n">
-        <v>369.4444444444444</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>477.2489580698352</v>
@@ -7985,7 +7985,7 @@
         <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O5" t="n">
         <v>455.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>369.7315044851259</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8684,10 +8684,10 @@
         <v>559</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
         <v>70.24786957409245</v>
@@ -8696,7 +8696,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>313.9750954005603</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8930,10 +8930,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q14" t="n">
-        <v>193.2279078336117</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>637.6468801143703</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>370.361973797064</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>327.3708917050792</v>
       </c>
       <c r="P20" t="n">
-        <v>20.69228354680773</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,10 +9638,10 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>370.361973797064</v>
       </c>
       <c r="P23" t="n">
-        <v>136.6628946047192</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,22 +9863,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>460.3127370737905</v>
+        <v>803.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>591.2181271554637</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,7 +10100,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>195.6693367737158</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,10 +10112,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>803.2478695740924</v>
+        <v>265.9172063478081</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>733.2870600406815</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,25 +10337,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
         <v>733</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>737.6034075115851</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>803.2478695740924</v>
+        <v>387.3332081078636</v>
       </c>
       <c r="P32" t="n">
-        <v>733.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
@@ -10583,16 +10583,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10820,16 +10820,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>661.3924512348954</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,16 +11045,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>685.4145387153925</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
@@ -11063,7 +11063,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>172.8226843274854</v>
@@ -11285,7 +11285,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11294,13 +11294,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O44" t="n">
-        <v>370.361973797064</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22709,7 +22709,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5911706460559</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646046521</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -24602,16 +24602,16 @@
         <v>218.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>269.1850752716849</v>
       </c>
       <c r="O28" t="n">
         <v>338.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>385.4478973282775</v>
+        <v>120.899766540631</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.636944484038395</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -24833,28 +24833,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>121.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>14.45696031775887</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>269.1850752716849</v>
       </c>
       <c r="O31" t="n">
         <v>338.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>385.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>305.6619533914939</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>424.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>60.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>121.5476281577792</v>
       </c>
       <c r="M34" t="n">
         <v>218.6316114025499</v>
@@ -25079,16 +25079,16 @@
         <v>269.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>338.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>385.4478973282775</v>
+        <v>120.899766540631</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>195.4450614491477</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>60.37347970285543</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2983140.73001022</v>
+        <v>2983140.730010219</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4943401.440707562</v>
+        <v>4943401.440707561</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5919418.646965322</v>
+        <v>5919418.646965321</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6895435.853223079</v>
+        <v>6895435.853223078</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7871453.059480836</v>
+        <v>7871453.059480835</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8834695.617792539</v>
+        <v>8834695.617792536</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9789711.877922421</v>
+        <v>9789711.877922419</v>
       </c>
     </row>
     <row r="12">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13664553.4586438</v>
+        <v>13664553.45864379</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14640570.66490157</v>
+        <v>14640570.66490156</v>
       </c>
     </row>
   </sheetData>
@@ -26284,10 +26284,10 @@
         <v>1227892.61432428</v>
       </c>
       <c r="G2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="H2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="I2" t="n">
         <v>1227892.61432428</v>
@@ -26296,22 +26296,22 @@
         <v>1201472.069195664</v>
       </c>
       <c r="K2" t="n">
-        <v>1201472.069195665</v>
+        <v>1201472.069195664</v>
       </c>
       <c r="L2" t="n">
-        <v>1201472.069195665</v>
+        <v>1201472.069195664</v>
       </c>
       <c r="M2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="N2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="O2" t="n">
+        <v>1227892.614324279</v>
+      </c>
+      <c r="P2" t="n">
         <v>1227892.61432428</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1227892.614324279</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>497080.9107622076</v>
+        <v>499048.7547001071</v>
       </c>
       <c r="K4" t="n">
-        <v>495312.6122507454</v>
+        <v>497280.4561886448</v>
       </c>
       <c r="L4" t="n">
-        <v>493541.8013236981</v>
+        <v>495509.6452615976</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>464385.6560316529</v>
+        <v>462869.8003433369</v>
       </c>
       <c r="C6" t="n">
-        <v>601963.6361654672</v>
+        <v>600447.7804771512</v>
       </c>
       <c r="D6" t="n">
-        <v>604024.4080777833</v>
+        <v>602508.5523894668</v>
       </c>
       <c r="E6" t="n">
-        <v>280139.2110977444</v>
+        <v>278397.361284637</v>
       </c>
       <c r="F6" t="n">
-        <v>623330.1064432486</v>
+        <v>621588.2566301408</v>
       </c>
       <c r="G6" t="n">
-        <v>625275.6829114341</v>
+        <v>623533.8330983262</v>
       </c>
       <c r="H6" t="n">
-        <v>627223.9597287356</v>
+        <v>625482.1099156275</v>
       </c>
       <c r="I6" t="n">
-        <v>629174.9563720956</v>
+        <v>627433.1065589882</v>
       </c>
       <c r="J6" t="n">
-        <v>196067.9204334564</v>
+        <v>194100.0764955574</v>
       </c>
       <c r="K6" t="n">
-        <v>636204.2189449194</v>
+        <v>634236.3750070197</v>
       </c>
       <c r="L6" t="n">
-        <v>637975.0298719668</v>
+        <v>636007.1859340669</v>
       </c>
       <c r="M6" t="n">
-        <v>598606.5397821789</v>
+        <v>596864.689969071</v>
       </c>
       <c r="N6" t="n">
-        <v>638971.4368170326</v>
+        <v>637229.5870039247</v>
       </c>
       <c r="O6" t="n">
-        <v>399339.1760747704</v>
+        <v>397597.3262616623</v>
       </c>
       <c r="P6" t="n">
-        <v>642909.7789257802</v>
+        <v>641167.929112673</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>48</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>302</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27045,7 +27045,7 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,13 +27518,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>172.5204020740694</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,13 +27569,13 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>15.21035976018675</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>317.2696668382184</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27594,31 +27594,31 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>276.0622769912434</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>372.2356904372914</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27752,25 +27752,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>177.0515108348265</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>214.7883661581947</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27834,28 +27834,28 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>326.3232931049183</v>
       </c>
       <c r="J7" t="n">
         <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27888,16 +27888,16 @@
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>215.232496909901</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>193.9840721817117</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>230.6029419303357</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28086,10 +28086,10 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28125,10 +28125,10 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>321.7065299027261</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>377.3873366464989</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
@@ -28159,13 +28159,13 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28241,7 +28241,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28268,16 +28268,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U12" t="n">
         <v>350</v>
@@ -28508,19 +28508,19 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T15" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W15" t="n">
         <v>350</v>
@@ -28636,10 +28636,10 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,10 +28697,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -28763,10 +28763,10 @@
         <v>350</v>
       </c>
       <c r="X18" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="C20" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28934,10 +28934,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -28955,7 +28955,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
-        <v>154.448623365906</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -29104,7 +29104,7 @@
         <v>350</v>
       </c>
       <c r="F23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G23" t="n">
         <v>350</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29177,7 +29177,7 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722602</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
@@ -29219,7 +29219,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
@@ -29234,10 +29234,10 @@
         <v>350</v>
       </c>
       <c r="W24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29259,58 +29259,58 @@
         <v>350</v>
       </c>
       <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="n">
+        <v>350</v>
+      </c>
+      <c r="G25" t="n">
+        <v>350</v>
+      </c>
+      <c r="H25" t="n">
+        <v>350</v>
+      </c>
+      <c r="I25" t="n">
+        <v>350</v>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+      <c r="K25" t="n">
+        <v>350</v>
+      </c>
+      <c r="L25" t="n">
+        <v>350</v>
+      </c>
+      <c r="M25" t="n">
+        <v>350</v>
+      </c>
+      <c r="N25" t="n">
+        <v>350</v>
+      </c>
+      <c r="O25" t="n">
+        <v>350</v>
+      </c>
+      <c r="P25" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>350</v>
+      </c>
+      <c r="R25" t="n">
+        <v>350</v>
+      </c>
+      <c r="S25" t="n">
+        <v>350</v>
+      </c>
+      <c r="T25" t="n">
+        <v>350</v>
+      </c>
+      <c r="U25" t="n">
+        <v>350</v>
+      </c>
+      <c r="V25" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="F25" t="n">
-        <v>350</v>
-      </c>
-      <c r="G25" t="n">
-        <v>350</v>
-      </c>
-      <c r="H25" t="n">
-        <v>350</v>
-      </c>
-      <c r="I25" t="n">
-        <v>350</v>
-      </c>
-      <c r="J25" t="n">
-        <v>350</v>
-      </c>
-      <c r="K25" t="n">
-        <v>350</v>
-      </c>
-      <c r="L25" t="n">
-        <v>350</v>
-      </c>
-      <c r="M25" t="n">
-        <v>350</v>
-      </c>
-      <c r="N25" t="n">
-        <v>350</v>
-      </c>
-      <c r="O25" t="n">
-        <v>350</v>
-      </c>
-      <c r="P25" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>350</v>
-      </c>
-      <c r="R25" t="n">
-        <v>350</v>
-      </c>
-      <c r="S25" t="n">
-        <v>350</v>
-      </c>
-      <c r="T25" t="n">
-        <v>350</v>
-      </c>
-      <c r="U25" t="n">
-        <v>350</v>
-      </c>
-      <c r="V25" t="n">
-        <v>350</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29444,10 +29444,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>250.460041825832</v>
       </c>
       <c r="O27" t="n">
-        <v>250.4600418258318</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -29587,7 +29587,7 @@
         <v>302</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>142.85656829727</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29626,7 +29626,7 @@
         <v>302</v>
       </c>
       <c r="V29" t="n">
-        <v>294.7754086145855</v>
+        <v>302</v>
       </c>
       <c r="W29" t="n">
         <v>302</v>
@@ -29821,10 +29821,10 @@
         <v>302</v>
       </c>
       <c r="H32" t="n">
-        <v>302</v>
+        <v>294.7754086145854</v>
       </c>
       <c r="I32" t="n">
-        <v>142.85656829727</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29918,10 +29918,10 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>250.460041825832</v>
       </c>
       <c r="O33" t="n">
-        <v>250.4600418258318</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -30125,10 +30125,10 @@
         <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>147.1207205878186</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30140,7 +30140,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,7 +30167,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>285.25992437226</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30204,7 +30204,7 @@
         <v>350</v>
       </c>
       <c r="D37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30295,7 +30295,7 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30362,7 +30362,7 @@
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30374,7 +30374,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30404,13 +30404,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="U39" t="n">
         <v>350</v>
@@ -30447,7 +30447,7 @@
         <v>350</v>
       </c>
       <c r="F40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30599,16 +30599,16 @@
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30799,10 +30799,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30833,7 +30833,7 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30890,7 +30890,7 @@
         <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -30899,7 +30899,7 @@
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
@@ -30936,7 +30936,7 @@
         <v>350</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34746,13 +34746,13 @@
         <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>369.4444444444444</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>385</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,31 +34880,31 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>3.33703034319877</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>162.2111239310337</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34989,19 +34989,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>385</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="O5" t="n">
         <v>385</v>
       </c>
       <c r="P5" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35120,28 +35120,28 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>149.6898374848</v>
       </c>
       <c r="J7" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35174,16 +35174,16 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>16.06218669368482</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35372,10 +35372,10 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35411,10 +35411,10 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>122.5362196865099</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>151.0145268077892</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -35463,10 +35463,10 @@
         <v>559</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35475,7 +35475,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>141.1524110730749</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -35709,10 +35709,10 @@
         <v>559</v>
       </c>
       <c r="P14" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="P17" t="n">
         <v>559</v>
-      </c>
-      <c r="L17" t="n">
-        <v>559.0000000000001</v>
-      </c>
-      <c r="M17" t="n">
-        <v>93.38475247205298</v>
-      </c>
-      <c r="N17" t="n">
-        <v>559</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="P20" t="n">
-        <v>20.40522350612631</v>
+        <v>559</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,10 +36417,10 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="P23" t="n">
         <v>559</v>
-      </c>
-      <c r="P23" t="n">
-        <v>136.3758345640378</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36545,7 +36545,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>61.23042579717762</v>
+        <v>69.01909516304346</v>
       </c>
       <c r="F25" t="n">
         <v>75.61714403225807</v>
@@ -36596,7 +36596,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36642,22 +36642,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>390.064867499698</v>
+        <v>733</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>590.9310671147822</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36730,10 +36730,10 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N27" t="n">
-        <v>134.6265501086548</v>
+        <v>385.0865919344868</v>
       </c>
       <c r="O27" t="n">
-        <v>491.9170637285782</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P27" t="n">
         <v>113.6660045146532</v>
@@ -36879,7 +36879,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>195.6693367737158</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,10 +36891,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
+        <v>195.6693367737157</v>
+      </c>
+      <c r="P29" t="n">
         <v>733</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -37116,25 +37116,25 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
         <v>733</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>260.3544494417499</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>733</v>
+        <v>317.0853385337711</v>
       </c>
       <c r="P32" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37204,10 +37204,10 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>134.6265501086548</v>
+        <v>385.0865919344868</v>
       </c>
       <c r="O33" t="n">
-        <v>491.9170637285782</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
         <v>113.6660045146532</v>
@@ -37350,7 +37350,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
@@ -37362,16 +37362,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37599,16 +37599,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37733,7 +37733,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G40" t="n">
         <v>104.95612715847</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>141.1524110730752</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
@@ -37842,7 +37842,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -38064,7 +38064,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -38073,13 +38073,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O44" t="n">
-        <v>300.1141042229716</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38222,7 +38222,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
